--- a/data/docs/财务/差旅报销标准.xlsx
+++ b/data/docs/财务/差旅报销标准.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,26 @@
           <t>市内交通补贴(元/天)</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>餐饮补贴(元/天)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>通讯补贴(元/天)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>一线城市</t>
+          <t>一线城市（北上广深）</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -445,31 +460,256 @@
       <c r="C2" t="n">
         <v>80</v>
       </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>普通员工标准</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>二线城市</t>
+          <t>新一线城市（杭州/成都/武汉/南京等）</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="C3" t="n">
-        <v>60</v>
+        <v>70</v>
+      </c>
+      <c r="D3" t="n">
+        <v>90</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>普通员工标准</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>三线及以下</t>
+          <t>二线城市（省会及计划单列市）</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>400</v>
+      </c>
+      <c r="C4" t="n">
+        <v>60</v>
+      </c>
+      <c r="D4" t="n">
+        <v>80</v>
+      </c>
+      <c r="E4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>普通员工标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>三线城市</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>300</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C5" t="n">
         <v>50</v>
+      </c>
+      <c r="D5" t="n">
+        <v>70</v>
+      </c>
+      <c r="E5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>普通员工标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>四线及以下城市</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>250</v>
+      </c>
+      <c r="C6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>普通员工标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>港澳台地区</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C7" t="n">
+        <v>150</v>
+      </c>
+      <c r="D7" t="n">
+        <v>200</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>普通员工标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>欧美地区（北美/欧洲/澳新）</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>200</v>
+      </c>
+      <c r="D8" t="n">
+        <v>250</v>
+      </c>
+      <c r="E8" t="n">
+        <v>80</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>普通员工标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>亚太地区（日韩/新加坡等）</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C9" t="n">
+        <v>150</v>
+      </c>
+      <c r="D9" t="n">
+        <v>200</v>
+      </c>
+      <c r="E9" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>普通员工标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>东南亚及其他地区</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>800</v>
+      </c>
+      <c r="C10" t="n">
+        <v>120</v>
+      </c>
+      <c r="D10" t="n">
+        <v>180</v>
+      </c>
+      <c r="E10" t="n">
+        <v>50</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>普通员工标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>副总及以上（国内）</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>800</v>
+      </c>
+      <c r="C11" t="n">
+        <v>120</v>
+      </c>
+      <c r="D11" t="n">
+        <v>150</v>
+      </c>
+      <c r="E11" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>高管标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>副总及以上（国际）</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C12" t="n">
+        <v>300</v>
+      </c>
+      <c r="D12" t="n">
+        <v>350</v>
+      </c>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>高管标准</t>
+        </is>
       </c>
     </row>
   </sheetData>
